--- a/Data/EventData/SDGE_2023.xlsx
+++ b/Data/EventData/SDGE_2023.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_55ACC047742EADE1E10E131A86198DDFABEA17D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E354CA7-4953-4CE7-8502-C32BDEA3C151}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CCA41E-E4C4-46B2-B74F-D12C42FC3731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interactive (2023)" sheetId="3" r:id="rId1"/>
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="151">
   <si>
     <t>Utility Name</t>
   </si>
@@ -969,15 +969,12 @@
   </si>
   <si>
     <t>USFS</t>
-  </si>
-  <si>
-    <t>This report includes SDG&amp;E’s preliminary assessment of the cause of the ignition; the cause of any ignition may remain subject to ongoing investigation by the appropriate fire investigation agency</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
@@ -1441,7 +1438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1644,9 +1641,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1763,7 +1757,9 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{8E5A7C82-9C55-472D-A3CD-E3C5E0B4EAB4}"/>
+  </tableStyles>
   <colors>
     <mruColors>
       <color rgb="FF00FFE5"/>
@@ -2071,74 +2067,74 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
-  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:W18"/>
+  <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" style="50" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="46" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="46" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.7109375" style="69" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="46" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="46" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.33203125" style="46" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="69" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.5546875" style="15" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.6640625" style="15" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="26" style="15" customWidth="1"/>
-    <col min="21" max="21" width="19.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.5703125" style="15" customWidth="1"/>
-    <col min="23" max="23" width="13.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.42578125" style="15"/>
+    <col min="21" max="21" width="19.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.5546875" style="15" customWidth="1"/>
+    <col min="23" max="23" width="13.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.44140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="88" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="91" t="s">
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="92"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="94" t="s">
+      <c r="I1" s="91"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="97" t="s">
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="80" t="s">
+      <c r="Q1" s="97"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="81"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="83"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="82"/>
     </row>
-    <row r="2" spans="1:23" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="87"/>
+    <row r="2" spans="1:23" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="86"/>
       <c r="B2" s="16" t="s">
         <v>6</v>
       </c>
@@ -2206,7 +2202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="61" t="s">
         <v>26</v>
       </c>
@@ -2273,7 +2269,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="61" t="s">
         <v>26</v>
       </c>
@@ -2340,7 +2336,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="61" t="s">
         <v>26</v>
       </c>
@@ -2405,7 +2401,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="61" t="s">
         <v>26</v>
       </c>
@@ -2472,7 +2468,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="61" t="s">
         <v>26</v>
       </c>
@@ -2541,7 +2537,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="61" t="s">
         <v>26</v>
       </c>
@@ -2600,7 +2596,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="61" t="s">
         <v>26</v>
       </c>
@@ -2669,7 +2665,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61" t="s">
         <v>26</v>
       </c>
@@ -2738,7 +2734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61" t="s">
         <v>26</v>
       </c>
@@ -2801,7 +2797,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="61" t="s">
         <v>26</v>
       </c>
@@ -2871,14 +2867,16 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61" t="s">
         <v>26</v>
       </c>
       <c r="B13" s="62">
         <v>45155</v>
       </c>
-      <c r="C13" s="49"/>
+      <c r="C13" s="49">
+        <v>0</v>
+      </c>
       <c r="D13" s="77" t="s">
         <v>90</v>
       </c>
@@ -2938,7 +2936,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="61" t="s">
         <v>26</v>
       </c>
@@ -3001,7 +2999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="61" t="s">
         <v>26</v>
       </c>
@@ -3066,7 +3064,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="61" t="s">
         <v>26</v>
       </c>
@@ -3133,7 +3131,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="61" t="s">
         <v>26</v>
       </c>
@@ -3196,7 +3194,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="61" t="s">
         <v>26</v>
       </c>
@@ -3265,37 +3263,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A20" s="79" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="79"/>
-      <c r="S20" s="79"/>
-      <c r="T20" s="79"/>
-      <c r="U20" s="79"/>
-      <c r="V20" s="79"/>
-      <c r="W20" s="79"/>
-    </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="8">
-    <mergeCell ref="A20:W20"/>
+  <mergeCells count="7">
     <mergeCell ref="S1:W1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A1:A2"/>
@@ -3391,28 +3361,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:U18"/>
-  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="76.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="53" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.42578125" style="1"/>
+    <col min="13" max="13" width="29.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G1" s="74"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>100</v>
       </c>
@@ -3471,7 +3441,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>108</v>
       </c>
@@ -3531,7 +3501,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>110</v>
       </c>
@@ -3585,7 +3555,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>118</v>
       </c>
@@ -3624,7 +3594,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>121</v>
       </c>
@@ -3663,7 +3633,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>126</v>
       </c>
@@ -3696,7 +3666,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -3726,7 +3696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G9" s="73" t="s">
         <v>134</v>
       </c>
@@ -3747,7 +3717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G10" s="74" t="s">
         <v>138</v>
       </c>
@@ -3765,7 +3735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G11" s="74"/>
       <c r="M11" s="1" t="s">
         <v>142</v>
@@ -3778,7 +3748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G12" s="74"/>
       <c r="M12" s="1" t="s">
         <v>144</v>
@@ -3791,7 +3761,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="74"/>
       <c r="M13" s="1" t="s">
         <v>146</v>
@@ -3804,7 +3774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G14" s="74" t="s">
         <v>131</v>
       </c>
@@ -3816,7 +3786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G15" s="74"/>
       <c r="M15" s="1" t="s">
         <v>127</v>
@@ -3826,7 +3796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G16" s="74"/>
       <c r="M16" s="1" t="s">
         <v>61</v>
@@ -3836,7 +3806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="7:20" x14ac:dyDescent="0.3">
       <c r="G17" s="74"/>
       <c r="M17" s="1" t="s">
         <v>148</v>
@@ -3846,7 +3816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="7:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="7:20" x14ac:dyDescent="0.3">
       <c r="G18" s="74"/>
       <c r="T18" s="1">
         <f t="shared" si="0"/>
